--- a/analysis/main_tables/mse_table.xlsx
+++ b/analysis/main_tables/mse_table.xlsx
@@ -463,7 +463,7 @@
         <v>0.07729454616211583</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07651912608680006</v>
+        <v>0.07723103900594563</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>0.07949844646981874</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07823574883004092</v>
+        <v>0.0793933368200274</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>0.08083484371271089</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07969976409868626</v>
+        <v>0.08071646904641239</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>0.07862700020472366</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07763520775569017</v>
+        <v>0.07848525169503817</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>0.08309191886343829</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08263021887197465</v>
+        <v>0.08295769233715304</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>0.07326989763398079</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06029442217092444</v>
+        <v>0.06029442217092446</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06028782295564297</v>
+        <v>0.06025608408932925</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         <v>0.07106507919241614</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06999188082721414</v>
+        <v>0.07099990795242518</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +572,10 @@
         <v>0.08232982390562361</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07443543144589623</v>
+        <v>0.07443543144589622</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07264987319929</v>
+        <v>0.07427179006172348</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         <v>0.08168356783458355</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07320343774613458</v>
+        <v>0.07320343774613459</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07233005170190364</v>
+        <v>0.07306698234117925</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         <v>0.0902644403842173</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07719729761293938</v>
+        <v>0.07719729761293941</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07691627394795067</v>
+        <v>0.07710444064861023</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         <v>0.07476233464372814</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07467833568148227</v>
+        <v>0.07468501977556347</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         <v>0.07182983777736945</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06977740038161508</v>
+        <v>0.07177333980817276</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         <v>0.06905025671518641</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07202363464535218</v>
+        <v>0.07202363464535219</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06905231712819572</v>
+        <v>0.07196430820423395</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>0.07050635003272662</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06783051568692694</v>
+        <v>0.07044243888626163</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +684,10 @@
         <v>0.06876964778865602</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0696855860505106</v>
+        <v>0.06968558605051059</v>
       </c>
       <c r="D16" t="n">
-        <v>0.06795561670435361</v>
+        <v>0.06960697718245326</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +700,10 @@
         <v>0.07439006864650284</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07034781690958251</v>
+        <v>0.07034781690958253</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0688903766546794</v>
+        <v>0.07023854444796132</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>0.07324930055186388</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07202381469283513</v>
+        <v>0.07312068950510831</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>0.07505040202274707</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0742145230747908</v>
+        <v>0.07491240496584443</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>0.08537510424119467</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07373002956964288</v>
+        <v>0.07373002956964289</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07334387741481165</v>
+        <v>0.07359910614288688</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         <v>0.07513563475648484</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07493913472866838</v>
+        <v>0.07502511631377713</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07803030766595925</v>
+        <v>0.07802020755710587</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07134529350853232</v>
+        <v>0.07081018425509757</v>
       </c>
       <c r="D22" t="n">
-        <v>0.06886641041966188</v>
+        <v>0.0706474762101917</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08563169728915801</v>
+        <v>0.08562713546898953</v>
       </c>
       <c r="C23" t="n">
-        <v>0.07695866535414121</v>
+        <v>0.07711528435831476</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07461794539998461</v>
+        <v>0.07694139754119492</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.08983128431400769</v>
+        <v>0.08982329992578182</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08033063631815804</v>
+        <v>0.08027701071313023</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07996776824377196</v>
+        <v>0.08016392111852952</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.08584886838709019</v>
+        <v>0.08584497590277905</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07688491321267643</v>
+        <v>0.07673681612953624</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07674293204164766</v>
+        <v>0.07665339260463401</v>
       </c>
     </row>
   </sheetData>
